--- a/data/data_lci.xlsx
+++ b/data/data_lci.xlsx
@@ -8,31 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2865" documentId="11_F25DC773A252ABDACC104887411C794C5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ADBACDB-D7B4-47DD-B18F-3F33C87051C5}"/>
+  <xr:revisionPtr revIDLastSave="2902" documentId="11_F25DC773A252ABDACC104887411C794C5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC41A216-8A2C-490D-A21C-3E42F166CB09}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="Flowsheets" sheetId="25" r:id="rId2"/>
-    <sheet name="Associated_LCIs" sheetId="24" r:id="rId3"/>
-    <sheet name="Feuil1" sheetId="26" r:id="rId4"/>
-    <sheet name="metal_list" sheetId="12" state="hidden" r:id="rId5"/>
-    <sheet name="technology_list" sheetId="17" state="hidden" r:id="rId6"/>
-    <sheet name="Associated_LCIs_" sheetId="23" r:id="rId7"/>
-    <sheet name="LCIs_review" sheetId="20" r:id="rId8"/>
-    <sheet name="LCI_results" sheetId="21" r:id="rId9"/>
-    <sheet name="EI_markets_old" sheetId="4" state="hidden" r:id="rId10"/>
-    <sheet name="IEA_demand_OLD" sheetId="3" state="hidden" r:id="rId11"/>
-    <sheet name="IEA_raw_data_mineral" sheetId="6" state="hidden" r:id="rId12"/>
-    <sheet name="IEA_raw_data_tech" sheetId="7" state="hidden" r:id="rId13"/>
+    <sheet name="Feuil2" sheetId="27" r:id="rId3"/>
+    <sheet name="Associated_LCIs" sheetId="24" r:id="rId4"/>
+    <sheet name="Feuil1" sheetId="26" r:id="rId5"/>
+    <sheet name="metal_list" sheetId="12" state="hidden" r:id="rId6"/>
+    <sheet name="technology_list" sheetId="17" state="hidden" r:id="rId7"/>
+    <sheet name="Associated_LCIs_" sheetId="23" r:id="rId8"/>
+    <sheet name="LCIs_review" sheetId="20" r:id="rId9"/>
+    <sheet name="LCI_results" sheetId="21" r:id="rId10"/>
+    <sheet name="EI_markets_old" sheetId="4" state="hidden" r:id="rId11"/>
+    <sheet name="IEA_demand_OLD" sheetId="3" state="hidden" r:id="rId12"/>
+    <sheet name="IEA_raw_data_mineral" sheetId="6" state="hidden" r:id="rId13"/>
+    <sheet name="IEA_raw_data_tech" sheetId="7" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Associated_LCIs!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Associated_LCIs_!$A$1:$I$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">LCIs_review!$A$1:$L$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">metal_list!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">technology_list!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Associated_LCIs!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Associated_LCIs_!$A$1:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">LCIs_review!$A$1:$L$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">metal_list!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">technology_list!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2293" uniqueCount="504">
   <si>
     <t>Aluminium</t>
   </si>
@@ -1589,6 +1590,66 @@
   </si>
   <si>
     <t>Tester un mix synthetic/natural?</t>
+  </si>
+  <si>
+    <t>Mineral</t>
+  </si>
+  <si>
+    <t>Upstream reference product</t>
+  </si>
+  <si>
+    <t>Downstream product</t>
+  </si>
+  <si>
+    <t>Pathway</t>
+  </si>
+  <si>
+    <t>Crude cobalt hydroxide</t>
+  </si>
+  <si>
+    <t>Battery-grade cobalt sulfate</t>
+  </si>
+  <si>
+    <t>Cu–Co ore mining and processing followed by Co(OH)₂ refining to CoSO₄</t>
+  </si>
+  <si>
+    <t>Nickel concentrate</t>
+  </si>
+  <si>
+    <t>Battery-grade nickel sulfate</t>
+  </si>
+  <si>
+    <t>Commentaires</t>
+  </si>
+  <si>
+    <t>Importer inventaire du Ni institute de Istrate et al ? Pour le Canada prendre Roy + transformation en sulfate ?</t>
+  </si>
+  <si>
+    <t>Mix of li brine concentrate and spodumene concentrate?</t>
+  </si>
+  <si>
+    <t>Lithium global market from Lai et al</t>
+  </si>
+  <si>
+    <t>Graphite global market from Lai et al</t>
+  </si>
+  <si>
+    <t>Copy de l'inventaire Au vers Ca pour spodumene concentrate ? Création marché brine concentrate + spodumene concentrate ?</t>
+  </si>
+  <si>
+    <t>Natural graphite concentrate (Engels)</t>
+  </si>
+  <si>
+    <t>Copy de l'inventaire M+C de Cn pour Ca pour concentrate ? Et des autres étapes pour refining</t>
+  </si>
+  <si>
+    <t>Copper concentrate</t>
+  </si>
+  <si>
+    <t>Copper, cathode</t>
+  </si>
+  <si>
+    <t>EI ? Ou prendre MetalliCan pour cu concentrate? Plus haut au Ca que RoW</t>
   </si>
 </sst>
 </file>
@@ -3175,6 +3236,16 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B782D5F6-B8F2-43AE-AE61-B2128B07C5C1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A08B9A-D812-4FA0-9C19-5E3A58E1E967}">
   <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7510,7 +7581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E8778F-4920-4B98-BE30-ECCF54C61BB1}">
   <dimension ref="A1:CU178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28466,7 +28537,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9ECD9F4-F7DC-433E-8C33-8704B76AABEF}">
   <dimension ref="A1:W48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -30698,7 +30769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F25CE1A-1BDB-4E50-90FB-7A7AE02CB903}">
   <dimension ref="A1:T98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -34123,6 +34194,116 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4C8FF5-B954-4B6A-B414-2640FD835DB4}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="65.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="52" t="s">
+        <v>484</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>485</v>
+      </c>
+      <c r="C1" s="52" t="s">
+        <v>486</v>
+      </c>
+      <c r="D1" s="52" t="s">
+        <v>487</v>
+      </c>
+      <c r="E1" s="52" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>488</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>489</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C3" t="s">
+        <v>492</v>
+      </c>
+      <c r="E3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C4" t="s">
+        <v>496</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C5" t="s">
+        <v>497</v>
+      </c>
+      <c r="D5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>501</v>
+      </c>
+      <c r="C6" t="s">
+        <v>502</v>
+      </c>
+      <c r="E6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04BD5059-7381-4E0A-847C-C483A266A2DA}">
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -34547,7 +34728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68651FD1-AA61-41FB-B13B-DA406416589A}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -34683,7 +34864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D888401B-D10E-4787-BDCA-76926E364445}">
   <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -35166,7 +35347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED367550-17AA-4D03-86BE-763D64FA14C0}">
   <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -35333,7 +35514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BD48F6-A6AD-4786-A370-E98C01BA826A}">
   <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -35907,7 +36088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{685B0E1F-3EDF-40A3-9949-C4DAA3689949}">
   <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37305,14 +37486,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B782D5F6-B8F2-43AE-AE61-B2128B07C5C1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>